--- a/Pivot_Excel/Pivot_b.xlsx
+++ b/Pivot_Excel/Pivot_b.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OLAP\Pro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OLAP\Pro\Pivot_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5238E0F9-B524-4B29-B09C-281E3C23291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3472D44C-41DC-4AD6-A403-40A7FFB80E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-119" yWindow="-119" windowWidth="28741" windowHeight="16271" xr2:uid="{83B1245F-5C2A-4F2F-9DCC-380A46EB8FC3}"/>
+    <workbookView xWindow="-119" yWindow="-119" windowWidth="28741" windowHeight="16271" xr2:uid="{9E22D599-675A-4B30-A045-F05A78A95696}"/>
   </bookViews>
   <sheets>
-    <sheet name="tmp6678" sheetId="1" r:id="rId1"/>
+    <sheet name="tmp95BC" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="90" r:id="rId2"/>
+    <pivotCache cacheId="165" r:id="rId2"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{11FE1B11-89C3-49EA-9BF5-ECDD582810B7}" odcFile="C:\Temp\tmp6678.odc" keepAlive="1" name="LAPTOP-40H784NV\SSASMD SSAS" type="5" refreshedVersion="8" background="1">
+  <connection id="1" xr16:uid="{FF1617A2-57E2-48E5-902B-B12840D5ECAE}" odcFile="C:\Temp\tmp95BC.odc" keepAlive="1" name="LAPTOP-40H784NV\SSASMD SSAS" type="5" refreshedVersion="8" background="1">
     <dbPr connection="Provider=MSOLAP.8;Integrated Security=SSPI;Persist Security Info=True;Initial Catalog=SSAS;Data Source=LAPTOP-40H784NV\SSASMD;MDX Compatibility=1;Safety Options=2;MDX Missing Member Mode=Error;Update Isolation Level=2" command="US Accidents DW" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
   </connection>
@@ -38,8 +38,8 @@
   </metadataTypes>
   <metadataStrings count="3">
     <s v="LAPTOP-40H784NV\SSASMD SSAS"/>
-    <s v="{[ID START DATE].[Hierarchy].[QUARTER].&amp;[2021]&amp;[2]}"/>
     <s v="{[DIM SEVERITY].[ID SEVERITY].&amp;[4]}"/>
+    <s v="{[ID START DATE].[YEAR].&amp;[2021]}"/>
   </metadataStrings>
   <mdxMetadata count="2">
     <mdx n="0" f="s">
@@ -61,192 +61,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>ID SEVERITY</t>
-  </si>
-  <si>
-    <t>ID START DATE.Hierarchy</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Fairfield</t>
-  </si>
-  <si>
-    <t>Clinton</t>
-  </si>
-  <si>
-    <t>Georgetown</t>
-  </si>
-  <si>
-    <t>Lancaster</t>
-  </si>
-  <si>
-    <t>Milford</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>Bristol</t>
-  </si>
-  <si>
-    <t>Lebanon</t>
-  </si>
-  <si>
-    <t>New Milford</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>Tyrone</t>
-  </si>
-  <si>
-    <t>Mount Pleasant</t>
-  </si>
-  <si>
-    <t>Brookville</t>
-  </si>
-  <si>
-    <t>Greencastle</t>
-  </si>
-  <si>
-    <t>Greensburg</t>
-  </si>
-  <si>
-    <t>Oil City</t>
-  </si>
-  <si>
-    <t>Hanover</t>
-  </si>
-  <si>
-    <t>Williamsport</t>
-  </si>
-  <si>
-    <t>Abbottstown</t>
-  </si>
-  <si>
-    <t>Ambler</t>
-  </si>
-  <si>
-    <t>Aston</t>
-  </si>
-  <si>
-    <t>Bernville</t>
-  </si>
-  <si>
-    <t>Centre Hall</t>
-  </si>
-  <si>
-    <t>Chambersburg</t>
-  </si>
-  <si>
-    <t>Dillsburg</t>
-  </si>
-  <si>
-    <t>Dushore</t>
-  </si>
-  <si>
-    <t>East Stroudsburg</t>
-  </si>
-  <si>
-    <t>Gettysburg</t>
-  </si>
-  <si>
-    <t>Glen Mills</t>
-  </si>
-  <si>
-    <t>Glenmoore</t>
-  </si>
-  <si>
-    <t>Hunker</t>
-  </si>
-  <si>
-    <t>Kinzers</t>
-  </si>
-  <si>
-    <t>Kunkletown</t>
-  </si>
-  <si>
-    <t>Lewis Run</t>
-  </si>
-  <si>
-    <t>Manheim</t>
-  </si>
-  <si>
-    <t>Mc Clure</t>
-  </si>
-  <si>
-    <t>Mc Connellsburg</t>
-  </si>
-  <si>
-    <t>Meyersdale</t>
-  </si>
-  <si>
-    <t>Muncy</t>
-  </si>
-  <si>
-    <t>New Oxford</t>
-  </si>
-  <si>
-    <t>Oakmont</t>
-  </si>
-  <si>
-    <t>Philadelphia</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Pittsburgh</t>
-  </si>
-  <si>
-    <t>Quakertown</t>
-  </si>
-  <si>
-    <t>Ringtown</t>
-  </si>
-  <si>
-    <t>Roaring Branch</t>
-  </si>
-  <si>
-    <t>Robesonia</t>
-  </si>
-  <si>
-    <t>Scott Township</t>
-  </si>
-  <si>
-    <t>Scranton</t>
-  </si>
-  <si>
-    <t>Sewickley</t>
-  </si>
-  <si>
-    <t>Tarentum</t>
-  </si>
-  <si>
-    <t>Trout Run</t>
-  </si>
-  <si>
-    <t>Ulster</t>
-  </si>
-  <si>
-    <t>Wellsboro</t>
   </si>
   <si>
     <t>FACT ACCIDENT Count</t>
   </si>
   <si>
-    <t>2</t>
+    <t>ID SEVERITY</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>ID START DATE.YEAR</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>PA</t>
   </si>
 </sst>
 </file>
@@ -751,13 +589,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -803,7 +641,38 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -817,121 +686,39 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Le Tan Vi" refreshedDate="46303.369716319445" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{059FF830-4A05-4DB6-B133-AFF5AC4E739F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Le Tan Vi" refreshedDate="46310.741851041668" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{27168B3D-6DCF-484E-85E4-75629E588CCC}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="13">
+  <cacheFields count="6">
+    <cacheField name="[Top_City_Severity4_Year2021]" caption="Top_City_Severity4_Year2021" numFmtId="0" hierarchy="83">
+      <sharedItems count="1">
+        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Allegheny]&amp;[Pittsburgh]" c="Pittsburgh"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[DIM LOCATION].[STATE].[STATE]" caption="STATE" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems count="1">
+        <s v="[DIM LOCATION].[STATE].&amp;[PA]" c="PA"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[FACT ACCIDENT Count]" caption="FACT ACCIDENT Count" numFmtId="0" hierarchy="74" level="32767"/>
     <cacheField name="[DIM SEVERITY].[ID SEVERITY].[ID SEVERITY]" caption="ID SEVERITY" numFmtId="0" hierarchy="15" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
     <cacheField name="[DIM SEVERITY].[ID SEVERITY].[ID SEVERITY].[SEVERITY DESC]" caption="SEVERITY DESC" propertyName="SEVERITY DESC" numFmtId="0" hierarchy="15" level="1" memberPropertyField="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[YEAR]" caption="YEAR" numFmtId="0" hierarchy="46" level="1">
+    <cacheField name="[ID START DATE].[YEAR].[YEAR]" caption="YEAR" numFmtId="0" hierarchy="51" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[QUARTER]" caption="QUARTER" numFmtId="0" hierarchy="46" level="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[MONTH]" caption="MONTH" numFmtId="0" hierarchy="46" level="3">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[DAY]" caption="DAY" numFmtId="0" hierarchy="46" level="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[QUARTER].[YEAR]" caption="YEAR" propertyName="YEAR" numFmtId="0" hierarchy="46" level="2" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[MONTH].[QUARTER]" caption="QUARTER" propertyName="QUARTER" numFmtId="0" hierarchy="46" level="3" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[ID START DATE].[Hierarchy].[DAY].[MONTH]" caption="MONTH" propertyName="MONTH" numFmtId="0" hierarchy="46" level="4" memberPropertyField="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[DIM LOCATION].[STATE].[STATE]" caption="STATE" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="1">
-        <s v="[DIM LOCATION].[STATE].&amp;[PA]" c="PA"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[DIM LOCATION].[CITY].[CITY]" caption="CITY" numFmtId="0" level="1" mappingCount="1">
-      <sharedItems count="54">
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Abbottstown]" c="Abbottstown"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Ambler]" c="Ambler"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Aston]" c="Aston"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Berlin]" c="Berlin"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Bernville]" c="Bernville"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Bristol]" c="Bristol"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Brookville]" c="Brookville"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Centre Hall]" c="Centre Hall"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Chambersburg]" c="Chambersburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Clinton]" c="Clinton"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Dillsburg]" c="Dillsburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Dushore]" c="Dushore"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[East Stroudsburg]" c="East Stroudsburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Fairfield]" c="Fairfield"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Georgetown]" c="Georgetown"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Gettysburg]" c="Gettysburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Glen Mills]" c="Glen Mills"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Glenmoore]" c="Glenmoore"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Greencastle]" c="Greencastle"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Greensburg]" c="Greensburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Hanover]" c="Hanover"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Hunker]" c="Hunker"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Kinzers]" c="Kinzers"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Kunkletown]" c="Kunkletown"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Lancaster]" c="Lancaster"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Lebanon]" c="Lebanon"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Lewis Run]" c="Lewis Run"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Manheim]" c="Manheim"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Mc Clure]" c="Mc Clure"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Mc Connellsburg]" c="Mc Connellsburg"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Meyersdale]" c="Meyersdale"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Milford]" c="Milford"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Mount Pleasant]" c="Mount Pleasant"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Muncy]" c="Muncy"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[New Milford]" c="New Milford"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[New Oxford]" c="New Oxford"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Oakmont]" c="Oakmont"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Oil City]" c="Oil City"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Philadelphia]" c="Philadelphia"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Pittsburgh]" c="Pittsburgh"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Quakertown]" c="Quakertown"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Ringtown]" c="Ringtown"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Roaring Branch]" c="Roaring Branch"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Robesonia]" c="Robesonia"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Scott Township]" c="Scott Township"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Scranton]" c="Scranton"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Sewickley]" c="Sewickley"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Tarentum]" c="Tarentum"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Trout Run]" c="Trout Run"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Tyrone]" c="Tyrone"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Ulster]" c="Ulster"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Washington]" c="Washington"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Wellsboro]" c="Wellsboro"/>
-        <s v="[DIM LOCATION].[CITY].&amp;[PA]&amp;[Williamsport]" c="Williamsport"/>
-      </sharedItems>
-      <mpMap v="11"/>
-    </cacheField>
-    <cacheField name="[DIM LOCATION].[CITY].[CITY].[STATE]" caption="STATE" propertyName="STATE" numFmtId="0" level="1" memberPropertyField="1">
-      <sharedItems count="1">
-        <s v="PA"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[FACT ACCIDENT Count]" caption="FACT ACCIDENT Count" numFmtId="0" hierarchy="74" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="75">
-    <cacheHierarchy uniqueName="[DIM LOCATION].[CITY]" caption="CITY" attribute="1" defaultMemberUniqueName="[DIM LOCATION].[CITY].[All]" allUniqueName="[DIM LOCATION].[CITY].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="10"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+  <cacheHierarchies count="84">
+    <cacheHierarchy uniqueName="[DIM LOCATION].[CITY]" caption="CITY" attribute="1" defaultMemberUniqueName="[DIM LOCATION].[CITY].[All]" allUniqueName="[DIM LOCATION].[CITY].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM LOCATION].[COUNTY]" caption="COUNTY" attribute="1" defaultMemberUniqueName="[DIM LOCATION].[COUNTY].[All]" allUniqueName="[DIM LOCATION].[COUNTY].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM LOCATION].[ID LOCATION]" caption="ID LOCATION" attribute="1" keyAttribute="1" defaultMemberUniqueName="[DIM LOCATION].[ID LOCATION].[All]" allUniqueName="[DIM LOCATION].[ID LOCATION].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[DIM LOCATION].[Location_BEF]" caption="Location_BEF" defaultMemberUniqueName="[DIM LOCATION].[Location_BEF].[All]" allUniqueName="[DIM LOCATION].[Location_BEF].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="4" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[DIM LOCATION].[Location_BEF]" caption="Location_BEF" defaultMemberUniqueName="[DIM LOCATION].[Location_BEF].[All]" allUniqueName="[DIM LOCATION].[Location_BEF].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM LOCATION].[STATE]" caption="STATE" attribute="1" defaultMemberUniqueName="[DIM LOCATION].[STATE].[All]" allUniqueName="[DIM LOCATION].[STATE].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="9"/>
+        <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[DIM LOCATION].[STREET]" caption="STREET" attribute="1" defaultMemberUniqueName="[DIM LOCATION].[STREET].[All]" allUniqueName="[DIM LOCATION].[STREET].[All]" dimensionUniqueName="[DIM LOCATION]" displayFolder="" count="0" unbalanced="0"/>
@@ -947,7 +734,7 @@
     <cacheHierarchy uniqueName="[DIM SEVERITY].[ID SEVERITY]" caption="ID SEVERITY" attribute="1" keyAttribute="1" defaultMemberUniqueName="[DIM SEVERITY].[ID SEVERITY].[All]" allUniqueName="[DIM SEVERITY].[ID SEVERITY].[All]" dimensionUniqueName="[DIM SEVERITY]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
+        <fieldUsage x="3"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[DIM SEVERITY].[SEVERITY DESC]" caption="SEVERITY DESC" attribute="1" defaultMemberUniqueName="[DIM SEVERITY].[SEVERITY DESC].[All]" allUniqueName="[DIM SEVERITY].[SEVERITY DESC].[All]" dimensionUniqueName="[DIM SEVERITY]" displayFolder="" count="0" unbalanced="0"/>
@@ -980,20 +767,17 @@
     <cacheHierarchy uniqueName="[ID START DATE].[DAY]" caption="ID START DATE.DAY" attribute="1" defaultMemberUniqueName="[ID START DATE].[DAY].[All]" allUniqueName="[ID START DATE].[DAY].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[DAY OF WEEK]" caption="ID START DATE.DAY OF WEEK" attribute="1" defaultMemberUniqueName="[ID START DATE].[DAY OF WEEK].[All]" allUniqueName="[ID START DATE].[DAY OF WEEK].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[FULL DATE]" caption="ID START DATE.FULL DATE" attribute="1" defaultMemberUniqueName="[ID START DATE].[FULL DATE].[All]" allUniqueName="[ID START DATE].[FULL DATE].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[ID START DATE].[Hierarchy]" caption="ID START DATE.Hierarchy" defaultMemberUniqueName="[ID START DATE].[Hierarchy].[All]" allUniqueName="[ID START DATE].[Hierarchy].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="5" unbalanced="0">
-      <fieldsUsage count="5">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-        <fieldUsage x="3"/>
-        <fieldUsage x="4"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[ID START DATE].[Hierarchy]" caption="ID START DATE.Hierarchy" defaultMemberUniqueName="[ID START DATE].[Hierarchy].[All]" allUniqueName="[ID START DATE].[Hierarchy].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[ID_DATE]" caption="ID START DATE.ID_DATE" attribute="1" keyAttribute="1" defaultMemberUniqueName="[ID START DATE].[ID_DATE].[All]" allUniqueName="[ID START DATE].[ID_DATE].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[IS WEEKEND]" caption="ID START DATE.IS WEEKEND" attribute="1" defaultMemberUniqueName="[ID START DATE].[IS WEEKEND].[All]" allUniqueName="[ID START DATE].[IS WEEKEND].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[MONTH]" caption="ID START DATE.MONTH" attribute="1" defaultMemberUniqueName="[ID START DATE].[MONTH].[All]" allUniqueName="[ID START DATE].[MONTH].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START DATE].[QUARTER]" caption="ID START DATE.QUARTER" attribute="1" defaultMemberUniqueName="[ID START DATE].[QUARTER].[All]" allUniqueName="[ID START DATE].[QUARTER].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[ID START DATE].[YEAR]" caption="ID START DATE.YEAR" attribute="1" defaultMemberUniqueName="[ID START DATE].[YEAR].[All]" allUniqueName="[ID START DATE].[YEAR].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[ID START DATE].[YEAR]" caption="ID START DATE.YEAR" attribute="1" defaultMemberUniqueName="[ID START DATE].[YEAR].[All]" allUniqueName="[ID START DATE].[YEAR].[All]" dimensionUniqueName="[ID START DATE]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[ID START TIME].[FULL TIME]" caption="ID START TIME.FULL TIME" attribute="1" defaultMemberUniqueName="[ID START TIME].[FULL TIME].[All]" allUniqueName="[ID START TIME].[FULL TIME].[All]" dimensionUniqueName="[ID START TIME]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START TIME].[Hierarchy]" caption="ID START TIME.Hierarchy" defaultMemberUniqueName="[ID START TIME].[Hierarchy].[All]" allUniqueName="[ID START TIME].[Hierarchy].[All]" dimensionUniqueName="[ID START TIME]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[ID START TIME].[HOUR]" caption="ID START TIME.HOUR" attribute="1" defaultMemberUniqueName="[ID START TIME].[HOUR].[All]" allUniqueName="[ID START TIME].[HOUR].[All]" dimensionUniqueName="[ID START TIME]" displayFolder="" count="0" unbalanced="0"/>
@@ -1018,8 +802,30 @@
     <cacheHierarchy uniqueName="[Measures].[PRECIPITATION]" caption="PRECIPITATION" measure="1" displayFolder="" measureGroup="FACT ACCIDENT" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[FACT ACCIDENT Count]" caption="FACT ACCIDENT Count" measure="1" displayFolder="" measureGroup="FACT ACCIDENT" count="0" oneField="1">
       <fieldsUsage count="1">
-        <fieldUsage x="12"/>
+        <fieldUsage x="2"/>
       </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[US_Junction]" caption="US_Junction" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[CA_Junction]" caption="CA_Junction" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[CA_Roundabout]" caption="CA_Roundabout" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[US_Roundabout]" caption="US_Roundabout" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[US_Railway]" caption="US_Railway" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[CA_Railway]" caption="CA_Railway" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[US_Traffic_Signal]" caption="US_Traffic_Signal" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[CA_Traffic_Signal]" caption="CA_Traffic_Signal" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Top_City_Severity4_Year2021]" caption="Top_City_Severity4_Year2021" set="1" parentSet="0" displayFolder="" count="0" unbalanced="0" unbalancedGroup="0">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{8CF416AD-EC4C-4aba-99F5-12A058AE0983}">
+          <x14:cacheHierarchy>
+            <x14:setLevels count="1">
+              <x14:setLevel hierarchy="0"/>
+            </x14:setLevels>
+          </x14:cacheHierarchy>
+        </ext>
+      </extLst>
     </cacheHierarchy>
   </cacheHierarchies>
   <kpis count="0"/>
@@ -1060,255 +866,33 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{445D5FB1-A99F-4759-BEE9-39FB865F9995}" name="PivotTable1" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A4:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
-    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B98BACA-54F6-49A0-94FE-BCCC8DD1BFB2}" name="PivotTable2" cacheId="165" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="City" fieldListSortAscending="1">
+  <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
       <items count="1">
-        <item s="1" x="0"/>
+        <item x="0"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="54">
+      <items count="1">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
       </items>
     </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" showPropTip="1"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="2">
-    <field x="9"/>
-    <field x="10"/>
+    <field x="0"/>
+    <field x="1"/>
   </rowFields>
-  <rowItems count="56">
+  <rowItems count="2">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
-    </i>
-    <i r="1">
-      <x v="20"/>
-    </i>
-    <i r="1">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="23"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i r="1">
-      <x v="25"/>
-    </i>
-    <i r="1">
-      <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="27"/>
-    </i>
-    <i r="1">
-      <x v="28"/>
-    </i>
-    <i r="1">
-      <x v="29"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i r="1">
-      <x v="31"/>
-    </i>
-    <i r="1">
-      <x v="32"/>
-    </i>
-    <i r="1">
-      <x v="33"/>
-    </i>
-    <i r="1">
-      <x v="34"/>
-    </i>
-    <i r="1">
-      <x v="35"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="37"/>
-    </i>
-    <i r="1">
-      <x v="38"/>
-    </i>
-    <i r="1">
-      <x v="39"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-    </i>
-    <i r="1">
-      <x v="42"/>
-    </i>
-    <i r="1">
-      <x v="43"/>
-    </i>
-    <i r="1">
-      <x v="44"/>
-    </i>
-    <i r="1">
-      <x v="45"/>
-    </i>
-    <i r="1">
-      <x v="46"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-    </i>
-    <i r="1">
-      <x v="48"/>
-    </i>
-    <i r="1">
-      <x v="49"/>
-    </i>
-    <i r="1">
-      <x v="50"/>
-    </i>
-    <i r="1">
-      <x v="51"/>
-    </i>
-    <i r="1">
-      <x v="52"/>
-    </i>
-    <i r="1">
-      <x v="53"/>
-    </i>
-    <i t="grand">
       <x/>
     </i>
   </rowItems>
@@ -1316,16 +900,31 @@
     <i/>
   </colItems>
   <pageFields count="2">
-    <pageField fld="2" hier="46" name="[ID START DATE].[Hierarchy].[QUARTER].&amp;[2021]&amp;[2]" cap="2"/>
-    <pageField fld="0" hier="15" name="[DIM SEVERITY].[ID SEVERITY].&amp;[4]" cap="4"/>
+    <pageField fld="3" hier="15" name="[DIM SEVERITY].[ID SEVERITY].&amp;[4]" cap="4"/>
+    <pageField fld="5" hier="51" name="[ID START DATE].[YEAR].&amp;[2021]" cap="2021"/>
   </pageFields>
   <dataFields count="1">
-    <dataField fld="12" baseField="0" baseItem="0"/>
+    <dataField fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotHierarchies count="75">
+  <pivotHierarchies count="84">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
     <pivotHierarchy>
       <mps count="1">
-        <mp field="11"/>
+        <mp field="4"/>
       </mps>
     </pivotHierarchy>
     <pivotHierarchy/>
@@ -1342,81 +941,65 @@
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy>
-      <mps count="1">
-        <mp field="1"/>
-      </mps>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy>
-      <mps count="3">
-        <mp field="6"/>
-        <mp field="7"/>
-        <mp field="8"/>
-      </mps>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="83"/>
     <rowHierarchyUsage hierarchyUsage="4"/>
-    <rowHierarchyUsage hierarchyUsage="0"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -1745,482 +1328,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5844B61D-9899-44E4-B622-08B6882EC147}">
-  <dimension ref="A1:B60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6678B698-B0EA-4E13-A3C7-5AE6970F5A3A}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.85" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s" vm="1">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s" vm="2">
-        <v>61</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
+      <c r="A5" s="3" t="s">
+        <v>0</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="B6" s="2">
         <v>18</v>
-      </c>
-      <c r="B24" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="4">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
